--- a/backend/scratch/daily-diary-csv/Daily_Diary_2026-06-19.xlsx
+++ b/backend/scratch/daily-diary-csv/Daily_Diary_2026-06-19.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="454">
   <si>
     <t>1. MANUAL FIR</t>
   </si>
@@ -89,6 +89,99 @@
     <t>PS Parliament Street</t>
   </si>
   <si>
+    <t>FIR/DD/2005</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Riverbank</t>
+  </si>
+  <si>
+    <t>Unidentified Body</t>
+  </si>
+  <si>
+    <t>FIR/DD/2006</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>Police</t>
+  </si>
+  <si>
+    <t>Old Town</t>
+  </si>
+  <si>
+    <t>Homicide reported, investigation on.</t>
+  </si>
+  <si>
+    <t>Vijay (absconding)</t>
+  </si>
+  <si>
+    <t>FIR/DD/2007</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>SHO</t>
+  </si>
+  <si>
+    <t>Highway Check Post</t>
+  </si>
+  <si>
+    <t>Contraband recovered.</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>FIR/DD/2008</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Pooja Rani</t>
+  </si>
+  <si>
+    <t>21, Lajpat Nagar</t>
+  </si>
+  <si>
+    <t>Metro Station</t>
+  </si>
+  <si>
+    <t>Mobile snatched and later recovered.</t>
+  </si>
+  <si>
+    <t>2. Details of E-Burglary Cases Registered in PS Gazipur</t>
+  </si>
+  <si>
+    <t>SR. NO.</t>
+  </si>
+  <si>
+    <t>E-FIR NO.</t>
+  </si>
+  <si>
+    <t>STOLEN ITEMS</t>
+  </si>
+  <si>
+    <t>IO NAME</t>
+  </si>
+  <si>
+    <t>IO MOBILE NO.</t>
+  </si>
+  <si>
+    <t>BEAT NO.</t>
+  </si>
+  <si>
     <t>FIR/DD/2001</t>
   </si>
   <si>
@@ -98,22 +191,28 @@
     <t>Anil Verma</t>
   </si>
   <si>
-    <t>Ram Verma</t>
-  </si>
-  <si>
     <t>12, Sector 5, New Delhi</t>
   </si>
   <si>
     <t>02:30</t>
   </si>
   <si>
+    <t>Gold jewellery, cash</t>
+  </si>
+  <si>
     <t>Sector 5 Market</t>
   </si>
   <si>
-    <t>House broken into overnight, valuables stolen.</t>
-  </si>
-  <si>
-    <t/>
+    <t>Insp. Rao</t>
+  </si>
+  <si>
+    <t>9811112222</t>
+  </si>
+  <si>
+    <t>B-11</t>
+  </si>
+  <si>
+    <t>2. Details of E-House Theft Cases Registered in Gazipur</t>
   </si>
   <si>
     <t>FIR/DD/2002</t>
@@ -125,19 +224,28 @@
     <t>Sunita Devi</t>
   </si>
   <si>
-    <t>Mohan Lal</t>
-  </si>
-  <si>
     <t>B-7, Green Park</t>
   </si>
   <si>
+    <t>Green Park</t>
+  </si>
+  <si>
     <t>14:00</t>
   </si>
   <si>
-    <t>Green Park</t>
-  </si>
-  <si>
-    <t>Theft from residence during day.</t>
+    <t>Laptop, watch</t>
+  </si>
+  <si>
+    <t>SI Khan</t>
+  </si>
+  <si>
+    <t>9822223333</t>
+  </si>
+  <si>
+    <t>B-3</t>
+  </si>
+  <si>
+    <t>2. Details of E-Other Theft Cases Registered in Gazipur</t>
   </si>
   <si>
     <t>FIR/DD/2003</t>
@@ -149,195 +257,78 @@
     <t>Rakesh Gupta</t>
   </si>
   <si>
-    <t>Suresh Gupta</t>
-  </si>
-  <si>
     <t>44, Karol Bagh</t>
   </si>
   <si>
     <t>19:45</t>
   </si>
   <si>
+    <t>Wallet</t>
+  </si>
+  <si>
     <t>Bus Stand</t>
   </si>
   <si>
-    <t>Pickpocketing at bus stand.</t>
+    <t>SI Meena</t>
+  </si>
+  <si>
+    <t>9833334444</t>
+  </si>
+  <si>
+    <t>B-9</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>dd</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>ff</t>
+  </si>
+  <si>
+    <t>2. Detail of MVT Cases Registered in PS Gazipur</t>
+  </si>
+  <si>
+    <t>SR.</t>
+  </si>
+  <si>
+    <t>DATE OF OCCURRENCE</t>
+  </si>
+  <si>
+    <t>VEHICLE NO.</t>
+  </si>
+  <si>
+    <t>VEHICLE TYPE</t>
+  </si>
+  <si>
+    <t>1ST CD UPLOADED IN 24 HRS (YES/NO)</t>
+  </si>
+  <si>
+    <t>WHETHER FOOTAGE IS COLLECTED OR NOT</t>
   </si>
   <si>
     <t>FIR/DD/2004</t>
   </si>
   <si>
+    <t>19/06/2026</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>Parking Lot A</t>
+  </si>
+  <si>
     <t>Deepak Singh</t>
   </si>
   <si>
-    <t>Harpal Singh</t>
-  </si>
-  <si>
     <t>9, Patel Nagar</t>
   </si>
   <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>Parking Lot A</t>
-  </si>
-  <si>
-    <t>FIR/DD/2005</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>Riverbank</t>
-  </si>
-  <si>
-    <t>Unidentified Body</t>
-  </si>
-  <si>
-    <t>FIR/DD/2006</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>Police</t>
-  </si>
-  <si>
-    <t>Old Town</t>
-  </si>
-  <si>
-    <t>Homicide reported, investigation on.</t>
-  </si>
-  <si>
-    <t>Vijay (absconding)</t>
-  </si>
-  <si>
-    <t>FIR/DD/2007</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>SHO</t>
-  </si>
-  <si>
-    <t>Highway Check Post</t>
-  </si>
-  <si>
-    <t>Contraband recovered.</t>
-  </si>
-  <si>
-    <t>FIR/DD/2008</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Pooja Rani</t>
-  </si>
-  <si>
-    <t>Ashok Rani</t>
-  </si>
-  <si>
-    <t>21, Lajpat Nagar</t>
-  </si>
-  <si>
-    <t>Metro Station</t>
-  </si>
-  <si>
-    <t>Mobile snatched and later recovered.</t>
-  </si>
-  <si>
-    <t>2. Details of E-Burglary Cases Registered in PS Gazipur</t>
-  </si>
-  <si>
-    <t>SR. NO.</t>
-  </si>
-  <si>
-    <t>E-FIR NO.</t>
-  </si>
-  <si>
-    <t>STOLEN ITEMS</t>
-  </si>
-  <si>
-    <t>IO NAME</t>
-  </si>
-  <si>
-    <t>IO MOBILE NO.</t>
-  </si>
-  <si>
-    <t>BEAT NO.</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Gold jewellery, cash</t>
-  </si>
-  <si>
-    <t>Insp. Rao</t>
-  </si>
-  <si>
-    <t>9811112222</t>
-  </si>
-  <si>
-    <t>B-11</t>
-  </si>
-  <si>
-    <t>2. Details of E-House Theft Cases Registered in Gazipur</t>
-  </si>
-  <si>
-    <t>Laptop, watch</t>
-  </si>
-  <si>
-    <t>SI Khan</t>
-  </si>
-  <si>
-    <t>9822223333</t>
-  </si>
-  <si>
-    <t>B-3</t>
-  </si>
-  <si>
-    <t>2. Details of E-Other Theft Cases Registered in Gazipur</t>
-  </si>
-  <si>
-    <t>Wallet</t>
-  </si>
-  <si>
-    <t>SI Meena</t>
-  </si>
-  <si>
-    <t>9833334444</t>
-  </si>
-  <si>
-    <t>B-9</t>
-  </si>
-  <si>
-    <t>2. Detail of MVT Cases Registered in PS Gazipur</t>
-  </si>
-  <si>
-    <t>SR.</t>
-  </si>
-  <si>
-    <t>DATE OF OCCURRENCE</t>
-  </si>
-  <si>
-    <t>VEHICLE NO.</t>
-  </si>
-  <si>
-    <t>VEHICLE TYPE</t>
-  </si>
-  <si>
-    <t>1ST CD UPLOADED IN 24 HRS (YES/NO)</t>
-  </si>
-  <si>
-    <t>WHETHER FOOTAGE IS COLLECTED OR NOT</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
     <t>DL3CAB1234</t>
   </si>
   <si>
@@ -353,7 +344,7 @@
     <t>B-2</t>
   </si>
   <si>
-    <t>YES</t>
+    <t>Yes</t>
   </si>
   <si>
     <t>3. Persons Arrested in All Heads (New Add Point) – Summary</t>
@@ -413,150 +404,123 @@
     <t>PO</t>
   </si>
   <si>
-    <t>7</t>
+    <t>4. Persons Arrested of East District in IPC/BNS &amp; ACT (Arms, Ex. Act, G.Act, NDPS &amp; Other Acts) Dated 12.06.2026</t>
+  </si>
+  <si>
+    <t>S.N.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FATHER/ HUSBAND NAME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDRESS </t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>NAME OF IO</t>
+  </si>
+  <si>
+    <t>PC/JC/BAIL</t>
+  </si>
+  <si>
+    <t>PREV. INVOLVEMENT (NO. OF CASES)</t>
+  </si>
+  <si>
+    <t>RECOVERY</t>
+  </si>
+  <si>
+    <t>WHETHER ACCUSED IS BC OR NOT</t>
+  </si>
+  <si>
+    <t>INTEGRATED PI</t>
+  </si>
+  <si>
+    <t>GROUP PATROLLING</t>
+  </si>
+  <si>
+    <t>CYCLE PATROLLING</t>
+  </si>
+  <si>
+    <t>BY ANTI-SNATCHING TEAM</t>
+  </si>
+  <si>
+    <t>BY PRAHARI</t>
+  </si>
+  <si>
+    <t>BY EYES &amp; EARS SCHEME MEMBERS</t>
+  </si>
+  <si>
+    <t>Vijay Kumar</t>
+  </si>
+  <si>
+    <t>Lala Kumar</t>
+  </si>
+  <si>
+    <t>Slum Area, Old Town</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Knife</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>DD/2010</t>
+  </si>
+  <si>
+    <t>126/170 BNSS</t>
+  </si>
+  <si>
+    <t>Mahesh Yadav</t>
+  </si>
+  <si>
+    <t>Ganga Yadav</t>
+  </si>
+  <si>
+    <t>Camp Road</t>
+  </si>
+  <si>
+    <t>Bound Down</t>
+  </si>
+  <si>
+    <t>EFIR Theft 2003</t>
+  </si>
+  <si>
+    <t>Sanjay Lal</t>
+  </si>
+  <si>
+    <t>Babu Lal</t>
+  </si>
+  <si>
+    <t>Karol Bagh</t>
+  </si>
+  <si>
+    <t>JC</t>
+  </si>
+  <si>
+    <t>EFIR MVT 2004</t>
+  </si>
+  <si>
+    <t>Imran Sheikh</t>
+  </si>
+  <si>
+    <t>Yusuf Sheikh</t>
+  </si>
+  <si>
+    <t>Patel Nagar</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>4. Persons Arrested of East District in IPC/BNS &amp; ACT (Arms, Ex. Act, G.Act, NDPS &amp; Other Acts) Dated 12.06.2026</t>
-  </si>
-  <si>
-    <t>S.N.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAME </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FATHER/ HUSBAND NAME </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDRESS </t>
-  </si>
-  <si>
-    <t>AGE</t>
-  </si>
-  <si>
-    <t>NAME OF IO</t>
-  </si>
-  <si>
-    <t>PC/JC/BAIL</t>
-  </si>
-  <si>
-    <t>PREV. INVOLVEMENT (NO. OF CASES)</t>
-  </si>
-  <si>
-    <t>RECOVERY</t>
-  </si>
-  <si>
-    <t>WHETHER ACCUSED IS BC OR NOT</t>
-  </si>
-  <si>
-    <t>INTEGRATED PI</t>
-  </si>
-  <si>
-    <t>GROUP PATROLLING</t>
-  </si>
-  <si>
-    <t>CYCLE PATROLLING</t>
-  </si>
-  <si>
-    <t>BY ANTI-SNATCHING TEAM</t>
-  </si>
-  <si>
-    <t>BY PRAHARI</t>
-  </si>
-  <si>
-    <t>BY EYES &amp; EARS SCHEME MEMBERS</t>
-  </si>
-  <si>
-    <t>Vijay Kumar</t>
-  </si>
-  <si>
-    <t>Lala Kumar</t>
-  </si>
-  <si>
-    <t>Slum Area, Old Town</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Knife</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>DD/2010</t>
-  </si>
-  <si>
-    <t>126/170 BNSS</t>
-  </si>
-  <si>
-    <t>Mahesh Yadav</t>
-  </si>
-  <si>
-    <t>Ganga Yadav</t>
-  </si>
-  <si>
-    <t>Camp Road</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Bound Down</t>
-  </si>
-  <si>
-    <t>EFIR Theft 2003</t>
-  </si>
-  <si>
-    <t>Sanjay Lal</t>
-  </si>
-  <si>
-    <t>Babu Lal</t>
-  </si>
-  <si>
-    <t>Karol Bagh</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>JC</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>EFIR MVT 2004</t>
-  </si>
-  <si>
-    <t>Imran Sheikh</t>
-  </si>
-  <si>
-    <t>Yusuf Sheikh</t>
-  </si>
-  <si>
-    <t>Patel Nagar</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>FIR/DD/1900</t>
   </si>
   <si>
@@ -566,18 +530,9 @@
     <t>Dhan Singh</t>
   </si>
   <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
     <t>po</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>FIR/DD/1850</t>
   </si>
   <si>
@@ -590,21 +545,12 @@
     <t>Bawana</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>Minor X</t>
   </si>
   <si>
     <t>Guardian Y</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>JJB</t>
   </si>
   <si>
@@ -623,15 +569,9 @@
     <t>Cyber Hub</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>Insp. Cyber</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>FIR/DD/2011</t>
   </si>
   <si>
@@ -647,15 +587,12 @@
     <t>Seelampur</t>
   </si>
   <si>
+    <t>DD/2012</t>
+  </si>
+  <si>
     <t>33</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>DD/2012</t>
-  </si>
-  <si>
     <t>Gopal Das</t>
   </si>
   <si>
@@ -665,15 +602,9 @@
     <t>Wazirpur</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
     <t>Bail</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>DD/2013</t>
   </si>
   <si>
@@ -689,12 +620,6 @@
     <t>Sadar Bazar</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>Sohan Singh</t>
   </si>
   <si>
@@ -704,9 +629,6 @@
     <t>Highway</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>5. Persons Arrested in Kalandara (126/170 BNSS, 40 Ex. Act, 92/93/97 DP Act)</t>
   </si>
   <si>
@@ -761,9 +683,6 @@
     <t>NAME OF COURT WHICH DECLARED PO</t>
   </si>
   <si>
-    <t>District Court</t>
-  </si>
-  <si>
     <t>9. Daily Action Against Listed Criminals</t>
   </si>
   <si>
@@ -812,9 +731,6 @@
     <t>REMARKS</t>
   </si>
   <si>
-    <t>BC</t>
-  </si>
-  <si>
     <t>10. District East – List of Arrested Persons for Last 24 Hours (Dt. 11.06.2026)</t>
   </si>
   <si>
@@ -857,21 +773,18 @@
     <t>CHALLAN / UNTRACE / CANCEL</t>
   </si>
   <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>Chargesheet</t>
-  </si>
-  <si>
-    <t>Chargesheeted</t>
-  </si>
-  <si>
-    <t>Closed</t>
+    <t>RC-1</t>
+  </si>
+  <si>
+    <t>Challan</t>
   </si>
   <si>
     <t>11. Daily Morning Dispose of PI Cases Diary – Disposal/Transfer of E-Property</t>
   </si>
   <si>
+    <t>10/06/2026</t>
+  </si>
+  <si>
     <t>11. Daily Morning Dispose of PI Cases Diary – Disposal/Transfer of E-MVT</t>
   </si>
   <si>
@@ -905,10 +818,16 @@
     <t>BRIEF FACTS/REMARKS</t>
   </si>
   <si>
-    <t>Minor</t>
-  </si>
-  <si>
-    <t>Pending JJB Order</t>
+    <t>First offender</t>
+  </si>
+  <si>
+    <t>IO &amp; JWO</t>
+  </si>
+  <si>
+    <t>Sent to Observation Home</t>
+  </si>
+  <si>
+    <t>Brief facts registered</t>
   </si>
   <si>
     <t>13. East Distt Daily Statement – Missing Persons</t>
@@ -968,112 +887,118 @@
     <t>DD/M/3001</t>
   </si>
   <si>
-    <t>hc_parliament_street</t>
+    <t>HC Ramesh</t>
   </si>
   <si>
     <t>Geeta Sharma</t>
   </si>
   <si>
-    <t>Tilak Nagar</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>165 cm</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
+    <t>Wheatish</t>
+  </si>
+  <si>
+    <t>Oval</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Clean Shaven</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>DD/M/3002</t>
+  </si>
+  <si>
+    <t>Rohit (minor)</t>
+  </si>
+  <si>
+    <t>DD/M/3003</t>
+  </si>
+  <si>
+    <t>Baby Anu</t>
+  </si>
+  <si>
+    <t>DD/M/3004</t>
+  </si>
+  <si>
+    <t>Kavya (minor)</t>
+  </si>
+  <si>
+    <t>13. East Distt Daily Statement – UIDB (Unidentified Dead Body)</t>
+  </si>
+  <si>
+    <t>FOUND PLACE</t>
+  </si>
+  <si>
+    <t>FOUND DATE</t>
+  </si>
+  <si>
+    <t>SEX</t>
+  </si>
+  <si>
+    <t>DD/U/4002</t>
+  </si>
+  <si>
+    <t>Ring Road</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>30-35</t>
+  </si>
+  <si>
+    <t>170 cm</t>
+  </si>
+  <si>
+    <t>Sallow</t>
+  </si>
+  <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>DD/U/4001</t>
+  </si>
+  <si>
+    <t>Yamuna Ghat</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>45-50</t>
+  </si>
+  <si>
+    <t>13. East Distt Daily Statement – Abandoned / Unconscious Children / Person</t>
+  </si>
+  <si>
+    <t>Railway Station</t>
+  </si>
+  <si>
+    <t>160 cm</t>
+  </si>
+  <si>
+    <t>Thin</t>
+  </si>
+  <si>
     <t>Fair</t>
   </si>
   <si>
-    <t>Oval</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>DD/M/3002</t>
-  </si>
-  <si>
-    <t>Rohit (minor)</t>
-  </si>
-  <si>
-    <t>Janakpuri</t>
-  </si>
-  <si>
-    <t>DD/M/3003</t>
-  </si>
-  <si>
-    <t>Baby Anu</t>
-  </si>
-  <si>
-    <t>DD/M/3004</t>
-  </si>
-  <si>
-    <t>Kavya (minor)</t>
-  </si>
-  <si>
-    <t>Dwarka</t>
-  </si>
-  <si>
-    <t>13. East Distt Daily Statement – UIDB (Unidentified Dead Body)</t>
-  </si>
-  <si>
-    <t>FOUND PLACE</t>
-  </si>
-  <si>
-    <t>FOUND DATE</t>
-  </si>
-  <si>
-    <t>SEX</t>
-  </si>
-  <si>
-    <t>DD/U/4001</t>
-  </si>
-  <si>
-    <t>Yamuna Ghat</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>45-50</t>
-  </si>
-  <si>
-    <t>170 cm</t>
-  </si>
-  <si>
-    <t>Wheatish</t>
-  </si>
-  <si>
-    <t>Round</t>
-  </si>
-  <si>
-    <t>Grey</t>
-  </si>
-  <si>
-    <t>DD/U/4002</t>
-  </si>
-  <si>
-    <t>Ring Road</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>30-35</t>
-  </si>
-  <si>
-    <t>13. East Distt Daily Statement – Abandoned / Unconscious Children / Person</t>
-  </si>
-  <si>
-    <t>Railway Station</t>
+    <t>Yellow</t>
   </si>
   <si>
     <t>13. East Distt Daily Statement – Traced Person</t>
@@ -1190,6 +1115,9 @@
     <t>NO. OF – 92/93/97 DP ACT</t>
   </si>
   <si>
+    <t>Nil</t>
+  </si>
+  <si>
     <t>16. Performa for Daily Morning Dairy for Inquest Registered (Dated 12.06.2026)</t>
   </si>
   <si>
@@ -1206,6 +1134,9 @@
   </si>
   <si>
     <t>GD/2005</t>
+  </si>
+  <si>
+    <t>Accidental</t>
   </si>
   <si>
     <t>16. Performa for Daily Morning Dairy for Disposal of Inquest Filed by ACP/SDM</t>
@@ -1248,19 +1179,58 @@
 (Property / Weapon / Cash etc.)</t>
   </si>
   <si>
-    <t>Burglary</t>
+    <t xml:space="preserve">THERE WILL BE 12 TABLES FOR THIS SCHEMA : </t>
+  </si>
+  <si>
+    <t>All Dacoity Cases</t>
+  </si>
+  <si>
+    <t>All Murder Cases</t>
+  </si>
+  <si>
+    <t>All Extortion Cases Involving Organized Gangs</t>
+  </si>
+  <si>
+    <t>All Cases Related to Members of Organized Gangs Operating in Delhi NCR</t>
+  </si>
+  <si>
+    <t>Attempt to Murder Cases Involving Firearms / Old Enmity / Rivalry</t>
+  </si>
+  <si>
+    <t>Politically / Communally / Religion Sensitive Cases</t>
+  </si>
+  <si>
+    <t>All Rape / POCSO Cases in Which Accused are Unknown</t>
+  </si>
+  <si>
+    <t>Robbery Cases in Which the Victim has Suffered Grievous Injuries</t>
+  </si>
+  <si>
+    <t>All Theft and Burglary Cases Including e-FIR Cases, in Which the Stolen Property Involved is More Than Rs. 50 Lakh</t>
+  </si>
+  <si>
+    <t>All ATM Breaking Cases</t>
+  </si>
+  <si>
+    <t>All Kidnapping for Ransom Cases</t>
+  </si>
+  <si>
+    <t>All Carjacking Cases</t>
+  </si>
+  <si>
+    <t>Murder</t>
   </si>
   <si>
     <t>New Delhi District</t>
   </si>
   <si>
-    <t>Murder</t>
-  </si>
-  <si>
     <t>Knife recovered</t>
   </si>
   <si>
     <t>Robbery</t>
+  </si>
+  <si>
+    <t>None Arrested</t>
   </si>
   <si>
     <t>Mobile phone (Samsung)</t>
@@ -1291,9 +1261,6 @@
 (E-FIR)</t>
   </si>
   <si>
-    <t>East District</t>
-  </si>
-  <si>
     <t>Accused Arrest Details in Financial Fraud Cases – PS Cyber East (Dt. 12.06.2026)</t>
   </si>
   <si>
@@ -1318,10 +1285,22 @@
     <t>RESPECTIVE ROLE OF ACCUSED</t>
   </si>
   <si>
-    <t>Zone-II</t>
-  </si>
-  <si>
-    <t>Eastern Range</t>
+    <t>Zone 2</t>
+  </si>
+  <si>
+    <t>New Delhi Range</t>
+  </si>
+  <si>
+    <t>Rs. 0</t>
+  </si>
+  <si>
+    <t>Cyber Fraud</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Primary Accused</t>
   </si>
   <si>
     <t>4. Patrolling &amp; Checking at Parks, Abandoned/Deserted Buildings etc.</t>
@@ -1379,7 +1358,7 @@
 (Bharatiya Nagarik Suraksha Sanhita – Use of Armed Force for Public Order)</t>
   </si>
   <si>
-    <t>2100 - 0000 Hrs</t>
+    <t>19:00 - 23:00 Hrs</t>
   </si>
   <si>
     <t>Daily Crime Reports of Eastern Range – Action under NDPS (Dt. 12.06.2026)</t>
@@ -1397,6 +1376,9 @@
     <t>PERSONS ARRESTED / BOUND DOWN</t>
   </si>
   <si>
+    <t>Ganja 2kg</t>
+  </si>
+  <si>
     <t>Daily Crime Reports of Eastern Range – Servant Verification (Dt. 12.06.2026)</t>
   </si>
   <si>
@@ -1436,12 +1418,6 @@
     <t>NAME OF POLICE OFFICER WHO RECOVERED THE MOBILE</t>
   </si>
   <si>
-    <t>Recovered</t>
-  </si>
-  <si>
-    <t>Handed Over</t>
-  </si>
-  <si>
     <t>Mobile Recovered – East District Summary (All Police Stations)</t>
   </si>
   <si>
@@ -1449,16 +1425,13 @@
   </si>
   <si>
     <t>MOBILE RECOVERED BY MOBILE TRACING TEAM</t>
-  </si>
-  <si>
-    <t>PS Gazipur</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1475,6 +1448,10 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -1529,7 +1506,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1576,6 +1553,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1590,20 +1582,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1906,7 +1898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
@@ -1990,31 +1982,31 @@
         <v>15</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="M3" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -2022,40 +2014,40 @@
         <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="M4" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -2063,40 +2055,40 @@
         <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -2104,204 +2096,40 @@
         <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2314,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -2332,7 +2160,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2357,102 +2185,49 @@
         <v>3</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="I2" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="L2" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="N2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="Q2" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2481,7 +2256,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2493,60 +2268,60 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>172</v>
+        <v>30</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>169</v>
+        <v>15</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2559,7 +2334,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2578,7 +2353,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2599,108 +2374,55 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>21</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -2727,7 +2449,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2742,496 +2464,496 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>143</v>
+        <v>137</v>
+      </c>
+      <c r="E3" s="5">
+        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L3" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>152</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>154</v>
+        <v>145</v>
+      </c>
+      <c r="E4" s="5">
+        <v>41</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>145</v>
+      <c r="A5" s="5">
+        <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>160</v>
+        <v>150</v>
+      </c>
+      <c r="E5" s="5">
+        <v>27</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>162</v>
+      <c r="A6" s="5">
+        <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="E6" s="5">
+        <v>29</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>168</v>
+      <c r="A7" s="5">
+        <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>173</v>
+        <v>30</v>
+      </c>
+      <c r="E7" s="5">
+        <v>38</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>175</v>
+      <c r="A8" s="5">
+        <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>180</v>
+        <v>164</v>
+      </c>
+      <c r="E8" s="5">
+        <v>44</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>121</v>
+      <c r="A9" s="5">
+        <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>184</v>
+        <v>150</v>
+      </c>
+      <c r="E9" s="5">
+        <v>16</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>181</v>
+      <c r="A10" s="5">
+        <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>191</v>
+        <v>172</v>
+      </c>
+      <c r="E10" s="5">
+        <v>30</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>193</v>
+      <c r="A11" s="5">
+        <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>199</v>
+        <v>178</v>
+      </c>
+      <c r="E11" s="5">
+        <v>33</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>200</v>
+      <c r="A12" s="5">
+        <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>205</v>
+        <v>183</v>
+      </c>
+      <c r="E12" s="5">
+        <v>36</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>207</v>
+      <c r="A13" s="5">
+        <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>213</v>
+        <v>189</v>
+      </c>
+      <c r="E13" s="5">
+        <v>39</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>214</v>
+      <c r="A14" s="5">
+        <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>218</v>
+        <v>192</v>
+      </c>
+      <c r="E14" s="5">
+        <v>31</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3244,7 +2966,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="14" customWidth="1"/>
@@ -3253,7 +2975,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3263,102 +2985,42 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>269</v>
+        <v>88</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3371,7 +3033,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="16" customWidth="1"/>
@@ -3380,7 +3042,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3390,62 +3052,82 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>269</v>
+        <v>88</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>148</v>
+      <c r="A4" s="5">
+        <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>269</v>
+        <v>88</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>272</v>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3467,7 +3149,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3477,42 +3159,42 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>269</v>
+        <v>88</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3543,7 +3225,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3560,90 +3242,90 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>269</v>
+        <v>88</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>184</v>
+        <v>256</v>
+      </c>
+      <c r="J3" s="5">
+        <v>16</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>85</v>
+        <v>257</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>21</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -3671,7 +3353,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3693,282 +3375,282 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="5">
+        <v>28</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="R3" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="5">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="C5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="5">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="C6" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>322</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>323</v>
+        <v>15</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>200</v>
+        <v>88</v>
+      </c>
+      <c r="H6" s="5">
+        <v>10</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3993,7 +3675,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4014,161 +3696,161 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="L2" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="C3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="E3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="I3" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>148</v>
+      <c r="A4" s="5">
+        <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>269</v>
+        <v>88</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>21</v>
+        <v>285</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -4196,7 +3878,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4211,13 +3893,13 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
@@ -4235,60 +3917,60 @@
         <v>7</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4313,7 +3995,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4333,102 +4015,102 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="F3" s="5">
+        <v>6</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -4453,7 +4135,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4464,80 +4146,80 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>317</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>148</v>
+      <c r="A4" s="5">
+        <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -4562,7 +4244,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4572,42 +4254,42 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>352</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4637,7 +4319,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4651,66 +4333,66 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>354</v>
+        <v>329</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>122</v>
+      <c r="A3" s="5">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4737,7 +4419,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>339</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4756,96 +4438,96 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>151</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>73</v>
+        <v>355</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>122</v>
+        <v>355</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>122</v>
+        <v>355</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>122</v>
+        <v>355</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>122</v>
+        <v>141</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>122</v>
+        <v>355</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>122</v>
+        <v>355</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4872,7 +4554,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4887,78 +4569,78 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>172</v>
+        <v>362</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -4984,7 +4666,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4998,72 +4680,72 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>269</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -5076,7 +4758,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="7" width="22" customWidth="1"/>
@@ -5086,7 +4768,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5101,31 +4783,31 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -5140,155 +4822,149 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="9" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="C4" s="8" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>1</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="D21" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>2</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
+      <c r="D22" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>393</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -5317,7 +4993,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5328,59 +5004,59 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="4" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" ht="40.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>181</v>
+      <c r="A4" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5411,7 +5087,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5426,72 +5102,72 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>269</v>
+        <v>88</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>73</v>
+        <v>413</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>21</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -5519,7 +5195,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5534,13 +5210,13 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
@@ -5561,63 +5237,63 @@
         <v>7</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5639,7 +5315,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5657,21 +5333,21 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="G2" s="4" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -5680,7 +5356,7 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="4" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -5688,79 +5364,79 @@
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="5">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="N3" s="8"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>122</v>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>9</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5790,7 +5466,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5800,42 +5476,42 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>73</v>
+        <v>389</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>73</v>
+        <v>437</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5857,7 +5533,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5868,48 +5544,48 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>446</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>122</v>
+        <v>389</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>15</v>
+      </c>
+      <c r="E3" s="5">
+        <v>345</v>
+      </c>
+      <c r="F3" s="5">
+        <v>220</v>
+      </c>
+      <c r="G3" s="5">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -5922,7 +5598,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5938,7 +5614,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5951,60 +5627,31 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -6017,7 +5664,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -6028,7 +5675,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6037,36 +5684,19 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>73</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -6088,7 +5718,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="14" customWidth="1"/>
@@ -6103,7 +5733,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6118,13 +5748,13 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
@@ -6142,60 +5772,101 @@
         <v>7</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>87</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -6224,7 +5895,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6243,7 +5914,7 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>1</v>
@@ -6255,7 +5926,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>7</v>
@@ -6273,78 +5944,78 @@
         <v>6</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>101</v>
+      <c r="Q3" s="5" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6375,7 +6046,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6397,114 +6068,114 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>120</v>
-      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>73</v>
+      <c r="A3" s="5">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6535,7 +6206,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6555,7 +6226,7 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -6564,721 +6235,721 @@
         <v>3</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="J2" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="K2" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="N2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="G3" s="5">
+        <v>32</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="L3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G4" s="5">
+        <v>41</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G5" s="5">
+        <v>27</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="5">
+        <v>29</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="5">
+        <v>38</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J7" s="5">
+        <v>5</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8" s="5">
+        <v>44</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8" s="5">
+        <v>8</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="G9" s="5">
+        <v>16</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G10" s="5">
+        <v>30</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J10" s="5">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G11" s="5">
+        <v>33</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="J11" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G12" s="5">
+        <v>36</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="I12" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="K12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G13" s="5">
+        <v>39</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="J13" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R13" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>218</v>
+      <c r="G14" s="5">
+        <v>31</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -7291,7 +6962,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
@@ -7311,7 +6982,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7332,120 +7003,132 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="L2" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="S2" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>154</v>
+        <v>145</v>
+      </c>
+      <c r="G3" s="5">
+        <v>41</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>21</v>
+        <v>146</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>147</v>
+        <v>141</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="V3" s="5">
+        <v>1</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -7458,7 +7141,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
@@ -7476,7 +7159,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7495,108 +7178,120 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="J2" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="M2" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="Q2" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="5">
+        <v>27</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="T3" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>147</v>
+      <c r="U3" s="5" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
